--- a/sub_pro_9_olympics_wpr_ioc/datasets/olympic_medal_country.xlsx
+++ b/sub_pro_9_olympics_wpr_ioc/datasets/olympic_medal_country.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\afrodataviz\sub_pro_9_olympics\processed_tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\carib_dataviz\sub_pro_9_olympics_wpr_ioc\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DAF443-5168-48EC-87B0-6C25FB7F6AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF2F070-B8DF-406C-A584-68DCF60F9358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1360" windowWidth="19200" windowHeight="7360" xr2:uid="{8F1463DF-6843-465E-9291-1B6CC41448CC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8F1463DF-6843-465E-9291-1B6CC41448CC}"/>
   </bookViews>
   <sheets>
     <sheet name="All countries" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="146">
   <si>
     <t>Country</t>
   </si>
@@ -451,9 +451,6 @@
     <t>Tonga</t>
   </si>
   <si>
-    <t>https://worldpopulationreview.com/country-rankings/olympic-medals-by-country</t>
-  </si>
-  <si>
     <t>Medals/Pop</t>
   </si>
   <si>
@@ -464,6 +461,9 @@
   </si>
   <si>
     <t>Medals per Person</t>
+  </si>
+  <si>
+    <t>2023 Population (world pop rev)</t>
   </si>
 </sst>
 </file>
@@ -824,1451 +824,1475 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D764ADDB-7834-4005-874E-3F921167113F}">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.36328125" customWidth="1"/>
     <col min="2" max="2" width="15.1796875" customWidth="1"/>
     <col min="3" max="3" width="9.90625" customWidth="1"/>
     <col min="5" max="5" width="13.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.08984375" customWidth="1"/>
+    <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.08984375" customWidth="1"/>
+    <col min="8" max="8" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1" t="s">
         <v>141</v>
+      </c>
+      <c r="H1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" t="s">
-        <v>143</v>
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>2980</v>
+      </c>
+      <c r="C2">
+        <v>1180</v>
+      </c>
+      <c r="D2">
+        <v>959</v>
+      </c>
+      <c r="E2">
+        <v>841</v>
+      </c>
+      <c r="F2" s="1">
+        <v>339996563</v>
+      </c>
+      <c r="G2">
+        <f>B2/F2</f>
+        <v>8.7647944841136526E-6</v>
+      </c>
+      <c r="H2">
+        <f>G2*100000</f>
+        <v>0.87647944841136527</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>2980</v>
+        <v>948</v>
       </c>
       <c r="C3">
-        <v>1180</v>
+        <v>296</v>
       </c>
       <c r="D3">
-        <v>959</v>
+        <v>320</v>
       </c>
       <c r="E3">
-        <v>841</v>
+        <v>332</v>
       </c>
       <c r="F3" s="1">
-        <v>339996563</v>
+        <v>67736802</v>
       </c>
       <c r="G3">
-        <f>B3/F3</f>
-        <v>8.7647944841136526E-6</v>
+        <f t="shared" ref="G3:G66" si="0">B3/F3</f>
+        <v>1.3995346281626936E-5</v>
       </c>
       <c r="H3">
-        <f>G3*100000</f>
-        <v>0.87647944841136527</v>
+        <f t="shared" ref="H3:H66" si="1">G3*100000</f>
+        <v>1.3995346281626935</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>948</v>
+        <v>892</v>
       </c>
       <c r="C4">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D4">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="E4">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="F4" s="1">
-        <v>67736802</v>
+        <v>83294633</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G67" si="0">B4/F4</f>
-        <v>1.3995346281626936E-5</v>
+        <f t="shared" si="0"/>
+        <v>1.0708973290031784E-5</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H67" si="1">G4*100000</f>
-        <v>1.3995346281626935</v>
+        <f t="shared" si="1"/>
+        <v>1.0708973290031785</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="C5">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="D5">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E5">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="F5" s="1">
-        <v>83294633</v>
+        <v>64756584</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>1.0708973290031784E-5</v>
+        <v>1.3496697108050048E-5</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>1.0708973290031785</v>
+        <v>1.3496697108050049</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>874</v>
+        <v>742</v>
       </c>
       <c r="C6">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D6">
-        <v>289</v>
+        <v>224</v>
       </c>
       <c r="E6">
-        <v>327</v>
+        <v>261</v>
       </c>
       <c r="F6" s="1">
-        <v>64756584</v>
+        <v>58870762</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>1.3496697108050048E-5</v>
+        <v>1.2603879664407945E-5</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>1.3496697108050049</v>
+        <v>1.2603879664407944</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7">
-        <v>742</v>
+        <v>696</v>
       </c>
       <c r="C7">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="D7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E7">
-        <v>261</v>
+        <v>194</v>
       </c>
       <c r="F7" s="1">
-        <v>58870762</v>
+        <v>1425671352</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>1.2603879664407945E-5</v>
+        <v>4.8819105400667408E-7</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>1.2603879664407944</v>
+        <v>4.881910540066741E-2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
-        <v>696</v>
+        <v>661</v>
       </c>
       <c r="C8">
-        <v>275</v>
+        <v>205</v>
       </c>
       <c r="D8">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E8">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="F8" s="1">
-        <v>1425671352</v>
+        <v>10612086</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>4.8819105400667408E-7</v>
+        <v>6.228747109663453E-5</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>4.881910540066741E-2</v>
+        <v>6.2287471096634528</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
-        <v>661</v>
+        <v>562</v>
       </c>
       <c r="C9">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="E9">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="F9" s="1">
-        <v>10612086</v>
+        <v>26439111</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>6.228747109663453E-5</v>
+        <v>2.1256387932256876E-5</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>6.2287471096634528</v>
+        <v>2.1256387932256877</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C10">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D10">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E10">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="F10" s="1">
-        <v>26439111</v>
+        <v>123294513</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>2.1256387932256876E-5</v>
+        <v>4.5014168635387694E-6</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>2.1256387932256877</v>
+        <v>0.45014168635387691</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C11">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D11">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E11">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="F11" s="1">
-        <v>123294513</v>
+        <v>144444359</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>4.5014168635387694E-6</v>
+        <v>3.7869253170350531E-6</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>0.45014168635387691</v>
+        <v>0.37869253170350531</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="C12">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D12">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E12">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="F12" s="1">
-        <v>144444359</v>
+        <v>5474360</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>3.7869253170350531E-6</v>
+        <v>9.6449630641755381E-5</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>0.37869253170350531</v>
+        <v>9.6449630641755384</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C13">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="D13">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E13">
-        <v>160</v>
+        <v>209</v>
       </c>
       <c r="F13" s="1">
-        <v>5474360</v>
+        <v>38781291</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>9.6449630641755381E-5</v>
+        <v>1.3537455470474151E-5</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>9.6449630641755384</v>
+        <v>1.3537455470474151</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C14">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="D14">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="E14">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="F14" s="1">
-        <v>38781291</v>
+        <v>10156239</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>1.3537455470474151E-5</v>
+        <v>5.1003132163392371E-5</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>1.3537455470474151</v>
+        <v>5.1003132163392371</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>518</v>
+        <v>472</v>
       </c>
       <c r="C15">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="D15">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E15">
         <v>180</v>
       </c>
       <c r="F15" s="1">
-        <v>10156239</v>
+        <v>5545475</v>
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>5.1003132163392371E-5</v>
+        <v>8.511444015165518E-5</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>5.1003132163392371</v>
+        <v>8.5114440151655177</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="C16">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D16">
         <v>148</v>
       </c>
       <c r="E16">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="F16" s="1">
-        <v>5545475</v>
+        <v>17618299</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>8.511444015165518E-5</v>
+        <v>2.5598384951918457E-5</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>8.5114440151655177</v>
+        <v>2.5598384951918458</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>451</v>
+        <v>358</v>
       </c>
       <c r="C17">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="D17">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E17">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="F17" s="1">
-        <v>17618299</v>
+        <v>8796669</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>2.5598384951918457E-5</v>
+        <v>4.069722300566271E-5</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>2.5598384951918458</v>
+        <v>4.069722300566271</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C18">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D18">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E18">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F18" s="1">
-        <v>8796669</v>
+        <v>51784059</v>
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>4.069722300566271E-5</v>
+        <v>6.8940134646455578E-6</v>
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>4.069722300566271</v>
+        <v>0.68940134646455575</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="C19">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="D19">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E19">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F19" s="1">
-        <v>51784059</v>
+        <v>8958960</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>6.8940134646455578E-6</v>
+        <v>3.6388152196237063E-5</v>
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>0.68940134646455575</v>
+        <v>3.6388152196237065</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C20">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D20">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E20">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="F20" s="1">
-        <v>8958960</v>
+        <v>41026067</v>
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>3.6388152196237063E-5</v>
+        <v>7.7999190124659041E-6</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>3.6388152196237065</v>
+        <v>0.77999190124659046</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C21">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D21">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="F21" s="1">
-        <v>41026067</v>
+        <v>19892812</v>
       </c>
       <c r="G21">
         <f t="shared" si="0"/>
-        <v>7.7999190124659041E-6</v>
+        <v>1.5533248894123165E-5</v>
       </c>
       <c r="H21">
         <f t="shared" si="1"/>
-        <v>0.77999190124659046</v>
+        <v>1.5533248894123164</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="C22">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D22">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="E22">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1">
-        <v>19892812</v>
+        <v>11194449</v>
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>1.5533248894123165E-5</v>
+        <v>2.1528527219160139E-5</v>
       </c>
       <c r="H22">
         <f t="shared" si="1"/>
-        <v>1.5533248894123164</v>
+        <v>2.1528527219160138</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C23">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E23">
         <v>85</v>
       </c>
       <c r="F23" s="1">
-        <v>11194449</v>
+        <v>6687717</v>
       </c>
       <c r="G23">
         <f t="shared" si="0"/>
-        <v>2.1528527219160139E-5</v>
+        <v>3.4391407411527728E-5</v>
       </c>
       <c r="H23">
         <f t="shared" si="1"/>
-        <v>2.1528527219160138</v>
+        <v>3.439140741152773</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C24">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D24">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E24">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F24" s="1">
-        <v>6687717</v>
+        <v>5910913</v>
       </c>
       <c r="G24">
         <f t="shared" si="0"/>
-        <v>3.4391407411527728E-5</v>
+        <v>3.4850792085757309E-5</v>
       </c>
       <c r="H24">
         <f t="shared" si="1"/>
-        <v>3.439140741152773</v>
+        <v>3.4850792085757307</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="C25">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D25">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E25">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="F25" s="1">
-        <v>5910913</v>
+        <v>47519628</v>
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>3.4850792085757309E-5</v>
+        <v>3.5985130186625199E-6</v>
       </c>
       <c r="H25">
         <f t="shared" si="1"/>
-        <v>3.4850792085757307</v>
+        <v>0.35985130186625197</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C26">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D26">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E26">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1">
-        <v>47519628</v>
+        <v>11686140</v>
       </c>
       <c r="G26">
         <f t="shared" si="0"/>
-        <v>3.5985130186625199E-6</v>
+        <v>1.3777004211827002E-5</v>
       </c>
       <c r="H26">
         <f t="shared" si="1"/>
-        <v>0.35985130186625197</v>
+        <v>1.3777004211827002</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C27">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D27">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E27">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F27" s="1">
-        <v>11686140</v>
+        <v>216422446</v>
       </c>
       <c r="G27">
         <f t="shared" si="0"/>
-        <v>1.3777004211827002E-5</v>
+        <v>6.93088922948408E-7</v>
       </c>
       <c r="H27">
         <f t="shared" si="1"/>
-        <v>1.3777004211827002</v>
+        <v>6.9308892294840801E-2</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C28">
+        <v>38</v>
+      </c>
+      <c r="D28">
         <v>37</v>
       </c>
-      <c r="D28">
-        <v>42</v>
-      </c>
       <c r="E28">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F28" s="1">
-        <v>216422446</v>
+        <v>36744634</v>
       </c>
       <c r="G28">
         <f t="shared" si="0"/>
-        <v>6.93088922948408E-7</v>
+        <v>4.0005841397141145E-6</v>
       </c>
       <c r="H28">
         <f t="shared" si="1"/>
-        <v>6.9308892294840801E-2</v>
+        <v>0.40005841397141145</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C29">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D29">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E29">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F29" s="1">
-        <v>36744634</v>
+        <v>5228100</v>
       </c>
       <c r="G29">
         <f t="shared" si="0"/>
-        <v>4.0005841397141145E-6</v>
+        <v>2.6778370727415312E-5</v>
       </c>
       <c r="H29">
         <f t="shared" si="1"/>
-        <v>0.40005841397141145</v>
+        <v>2.6778370727415313</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C30">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D30">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E30">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F30" s="1">
-        <v>5228100</v>
+        <v>10341277</v>
       </c>
       <c r="G30">
         <f t="shared" si="0"/>
-        <v>2.6778370727415312E-5</v>
+        <v>1.1700682613955705E-5</v>
       </c>
       <c r="H30">
         <f t="shared" si="1"/>
-        <v>2.6778370727415313</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31">
-        <v>121</v>
-      </c>
-      <c r="C31">
+        <v>1.1700682613955704</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D31">
-        <v>45</v>
-      </c>
-      <c r="E31">
+      <c r="B31" s="2">
+        <v>113</v>
+      </c>
+      <c r="C31" s="2">
+        <v>35</v>
+      </c>
+      <c r="D31" s="2">
+        <v>42</v>
+      </c>
+      <c r="E31" s="2">
+        <v>36</v>
+      </c>
+      <c r="F31" s="3">
+        <v>55100586</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="0"/>
+        <v>2.0507948862830604E-6</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="1"/>
+        <v>0.20507948862830605</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>104</v>
+      </c>
+      <c r="C32">
         <v>41</v>
       </c>
-      <c r="F31" s="1">
-        <v>10341277</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="0"/>
-        <v>1.1700682613955705E-5</v>
-      </c>
-      <c r="H31">
-        <f t="shared" si="1"/>
-        <v>1.1700682613955704</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="2">
-        <v>113</v>
-      </c>
-      <c r="C32" s="2">
-        <v>35</v>
-      </c>
-      <c r="D32" s="2">
-        <v>42</v>
-      </c>
-      <c r="E32" s="2">
-        <v>36</v>
-      </c>
-      <c r="F32" s="3">
-        <v>55100586</v>
-      </c>
-      <c r="G32" s="2">
-        <f t="shared" si="0"/>
-        <v>2.0507948862830604E-6</v>
-      </c>
-      <c r="H32" s="2">
-        <f t="shared" si="1"/>
-        <v>0.20507948862830605</v>
+      <c r="D32">
+        <v>26</v>
+      </c>
+      <c r="E32">
+        <v>37</v>
+      </c>
+      <c r="F32" s="1">
+        <v>85816199</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>1.2118924073996798E-6</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>0.12118924073996798</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D33">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F33" s="1">
-        <v>85816199</v>
+        <v>9498238</v>
       </c>
       <c r="G33">
         <f t="shared" si="0"/>
-        <v>1.2118924073996798E-6</v>
+        <v>1.0844116561408547E-5</v>
       </c>
       <c r="H33">
         <f t="shared" si="1"/>
-        <v>0.12118924073996798</v>
+        <v>1.0844116561408548</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C34">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D34">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E34">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F34" s="1">
-        <v>9498238</v>
+        <v>10495295</v>
       </c>
       <c r="G34">
         <f t="shared" si="0"/>
-        <v>1.0844116561408547E-5</v>
+        <v>9.3375174304295396E-6</v>
       </c>
       <c r="H34">
         <f t="shared" si="1"/>
-        <v>1.0844116561408548</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35">
-        <v>98</v>
-      </c>
-      <c r="C35">
-        <v>28</v>
-      </c>
-      <c r="D35">
-        <v>32</v>
-      </c>
-      <c r="E35">
-        <v>38</v>
-      </c>
-      <c r="F35" s="1">
-        <v>10495295</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="0"/>
-        <v>9.3375174304295396E-6</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="1"/>
         <v>0.93375174304295394</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+    <row r="35" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B35" s="2">
         <v>89</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C35" s="2">
         <v>27</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D35" s="2">
         <v>33</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E35" s="2">
         <v>29</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F35" s="3">
         <v>60414495</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G35" s="2">
         <f t="shared" si="0"/>
         <v>1.4731564006286903E-6</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H35" s="2">
         <f t="shared" si="1"/>
         <v>0.14731564006286901</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36">
+        <v>87</v>
+      </c>
+      <c r="C36">
+        <v>26</v>
+      </c>
+      <c r="D36">
+        <v>36</v>
+      </c>
+      <c r="E36">
+        <v>25</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2825544</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>3.079053095616278E-5</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>3.079053095616278</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>80</v>
+      </c>
+      <c r="C37">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>24</v>
+      </c>
+      <c r="E37">
         <v>40</v>
       </c>
-      <c r="B37">
-        <v>87</v>
-      </c>
-      <c r="C37">
-        <v>26</v>
-      </c>
-      <c r="D37">
-        <v>36</v>
-      </c>
-      <c r="E37">
-        <v>25</v>
-      </c>
       <c r="F37" s="1">
-        <v>2825544</v>
+        <v>19606633</v>
       </c>
       <c r="G37">
         <f t="shared" si="0"/>
-        <v>3.079053095616278E-5</v>
+        <v>4.0802518209016308E-6</v>
       </c>
       <c r="H37">
         <f t="shared" si="1"/>
-        <v>3.079053095616278</v>
+        <v>0.40802518209016309</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C38">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E38">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F38" s="1">
-        <v>19606633</v>
+        <v>45773884</v>
       </c>
       <c r="G38">
         <f t="shared" si="0"/>
-        <v>4.0802518209016308E-6</v>
+        <v>1.6821819184057004E-6</v>
       </c>
       <c r="H38">
         <f t="shared" si="1"/>
-        <v>0.40802518209016309</v>
+        <v>0.16821819184057005</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D39">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F39" s="1">
-        <v>45773884</v>
+        <v>89172767</v>
       </c>
       <c r="G39">
         <f t="shared" si="0"/>
-        <v>1.6821819184057004E-6</v>
+        <v>8.5227814002900684E-7</v>
       </c>
       <c r="H39">
         <f t="shared" si="1"/>
-        <v>0.16821819184057005</v>
+        <v>8.5227814002900679E-2</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B40">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C40">
+        <v>13</v>
+      </c>
+      <c r="D40">
         <v>24</v>
       </c>
-      <c r="D40">
+      <c r="E40">
+        <v>36</v>
+      </c>
+      <c r="F40" s="1">
+        <v>128455567</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>5.6828988968613563E-7</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>5.6828988968613561E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="2">
+        <v>58</v>
+      </c>
+      <c r="C41" s="2">
         <v>23</v>
       </c>
-      <c r="E40">
-        <v>29</v>
-      </c>
-      <c r="F40" s="1">
-        <v>89172767</v>
-      </c>
-      <c r="G40">
-        <f t="shared" si="0"/>
-        <v>8.5227814002900684E-7</v>
-      </c>
-      <c r="H40">
-        <f t="shared" si="1"/>
-        <v>8.5227814002900679E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41">
-        <v>73</v>
-      </c>
-      <c r="C41">
-        <v>13</v>
-      </c>
-      <c r="D41">
-        <v>24</v>
-      </c>
-      <c r="E41">
-        <v>36</v>
-      </c>
-      <c r="F41" s="1">
-        <v>128455567</v>
-      </c>
-      <c r="G41">
-        <f t="shared" si="0"/>
-        <v>5.6828988968613563E-7</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="1"/>
-        <v>5.6828988968613561E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="2">
-        <v>58</v>
-      </c>
-      <c r="C42" s="2">
+      <c r="D41" s="2">
+        <v>12</v>
+      </c>
+      <c r="E41" s="2">
         <v>23</v>
       </c>
-      <c r="D42" s="2">
-        <v>12</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="F41" s="3">
+        <v>126527060</v>
+      </c>
+      <c r="G41" s="2">
+        <f t="shared" si="0"/>
+        <v>4.5839996598356117E-7</v>
+      </c>
+      <c r="H41" s="2">
+        <f t="shared" si="1"/>
+        <v>4.5839996598356116E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42">
+        <v>56</v>
+      </c>
+      <c r="C42">
+        <v>16</v>
+      </c>
+      <c r="D42">
+        <v>17</v>
+      </c>
+      <c r="E42">
         <v>23</v>
       </c>
-      <c r="F42" s="3">
-        <v>126527060</v>
-      </c>
-      <c r="G42" s="2">
-        <f t="shared" si="0"/>
-        <v>4.5839996598356117E-7</v>
-      </c>
-      <c r="H42" s="2">
-        <f t="shared" si="1"/>
-        <v>4.5839996598356116E-2</v>
+      <c r="F42" s="1">
+        <v>26160821</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>2.1406056025535285E-6</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>0.21406056025535286</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B43">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D43">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1">
-        <v>26160821</v>
+        <v>4008617</v>
       </c>
       <c r="G43">
         <f t="shared" si="0"/>
-        <v>2.1406056025535285E-6</v>
+        <v>1.2972054950622622E-5</v>
       </c>
       <c r="H43">
         <f t="shared" si="1"/>
-        <v>0.21406056025535286</v>
+        <v>1.2972054950622622</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B44">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C44">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F44" s="1">
-        <v>4008617</v>
+        <v>10412651</v>
       </c>
       <c r="G44">
         <f t="shared" si="0"/>
-        <v>1.2972054950622622E-5</v>
+        <v>4.705814110162724E-6</v>
       </c>
       <c r="H44">
         <f t="shared" si="1"/>
-        <v>1.2972054950622622</v>
+        <v>0.47058141101627238</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B45">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>14</v>
       </c>
       <c r="E45">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F45" s="1">
-        <v>10412651</v>
+        <v>2119675</v>
       </c>
       <c r="G45">
         <f t="shared" si="0"/>
-        <v>4.705814110162724E-6</v>
+        <v>2.1229669642751836E-5</v>
       </c>
       <c r="H45">
         <f t="shared" si="1"/>
-        <v>0.47058141101627238</v>
+        <v>2.1229669642751836</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B46">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D46">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1">
-        <v>2119675</v>
+        <v>1322765</v>
       </c>
       <c r="G46">
         <f t="shared" si="0"/>
-        <v>2.1229669642751836E-5</v>
+        <v>3.2507663870755575E-5</v>
       </c>
       <c r="H46">
         <f t="shared" si="1"/>
-        <v>2.1229669642751836</v>
+        <v>3.2507663870755574</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B47">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E47">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1">
-        <v>1322765</v>
+        <v>5795199</v>
       </c>
       <c r="G47">
         <f t="shared" si="0"/>
-        <v>3.2507663870755575E-5</v>
+        <v>6.9022651336045575E-6</v>
       </c>
       <c r="H47">
         <f t="shared" si="1"/>
-        <v>3.2507663870755574</v>
+        <v>0.69022651336045571</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>40</v>
       </c>
       <c r="C48">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D48">
+        <v>12</v>
+      </c>
+      <c r="E48">
         <v>18</v>
       </c>
-      <c r="E48">
-        <v>9</v>
-      </c>
       <c r="F48" s="1">
-        <v>5795199</v>
+        <v>3728282</v>
       </c>
       <c r="G48">
         <f t="shared" si="0"/>
-        <v>6.9022651336045575E-6</v>
+        <v>1.0728802166788885E-5</v>
       </c>
       <c r="H48">
         <f t="shared" si="1"/>
-        <v>0.69022651336045571</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49">
-        <v>40</v>
-      </c>
-      <c r="C49">
-        <v>10</v>
-      </c>
-      <c r="D49">
-        <v>12</v>
-      </c>
-      <c r="E49">
-        <v>18</v>
-      </c>
-      <c r="F49" s="1">
-        <v>3728282</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="0"/>
-        <v>1.0728802166788885E-5</v>
-      </c>
-      <c r="H49">
-        <f t="shared" si="1"/>
         <v>1.0728802166788884</v>
       </c>
     </row>
-    <row r="50" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
+    <row r="49" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B49" s="2">
         <v>38</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C49" s="2">
         <v>8</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D49" s="2">
         <v>11</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E49" s="2">
         <v>19</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F49" s="3">
         <v>112716598</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G49" s="2">
         <f t="shared" si="0"/>
         <v>3.3712869865004267E-7</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H49" s="2">
         <f t="shared" si="1"/>
         <v>3.3712869865004269E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50">
+        <v>37</v>
+      </c>
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>14</v>
+      </c>
+      <c r="E50">
+        <v>15</v>
+      </c>
+      <c r="F50" s="1">
+        <v>277534122</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>1.3331694039408965E-7</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>1.3331694039408964E-2</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B51">
         <v>37</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D51">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1">
-        <v>277534122</v>
+        <v>35163944</v>
       </c>
       <c r="G51">
         <f t="shared" si="0"/>
-        <v>1.3331694039408965E-7</v>
+        <v>1.0522141657374952E-6</v>
       </c>
       <c r="H51">
         <f t="shared" si="1"/>
-        <v>1.3331694039408964E-2</v>
+        <v>0.10522141657374952</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B52">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C52">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E52">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F52" s="1">
-        <v>35163944</v>
+        <v>1428627663</v>
       </c>
       <c r="G52">
         <f t="shared" si="0"/>
-        <v>1.0522141657374952E-6</v>
+        <v>2.449903561751205E-8</v>
       </c>
       <c r="H52">
         <f t="shared" si="1"/>
-        <v>0.10522141657374952</v>
+        <v>2.4499035617512048E-3</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B53">
         <v>35</v>
@@ -2277,306 +2301,306 @@
         <v>10</v>
       </c>
       <c r="D53">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F53" s="1">
-        <v>1428627663</v>
+        <v>71801279</v>
       </c>
       <c r="G53">
         <f t="shared" si="0"/>
-        <v>2.449903561751205E-8</v>
+        <v>4.8745649781531055E-7</v>
       </c>
       <c r="H53">
         <f t="shared" si="1"/>
-        <v>2.4499035617512048E-3</v>
+        <v>4.8745649781531057E-2</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>35</v>
       </c>
       <c r="C54">
+        <v>11</v>
+      </c>
+      <c r="D54">
         <v>10</v>
       </c>
-      <c r="D54">
-        <v>8</v>
-      </c>
       <c r="E54">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1">
-        <v>71801279</v>
+        <v>5056935</v>
       </c>
       <c r="G54">
         <f t="shared" si="0"/>
-        <v>4.8745649781531055E-7</v>
+        <v>6.9211884273774527E-6</v>
       </c>
       <c r="H54">
         <f t="shared" si="1"/>
-        <v>4.8745649781531057E-2</v>
+        <v>0.69211884273774527</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B55">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E55">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F55" s="1">
-        <v>5056935</v>
+        <v>52085168</v>
       </c>
       <c r="G55">
         <f t="shared" si="0"/>
-        <v>6.9211884273774527E-6</v>
+        <v>6.5277700553831372E-7</v>
       </c>
       <c r="H55">
         <f t="shared" si="1"/>
-        <v>0.69211884273774527</v>
+        <v>6.5277700553831378E-2</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B56">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E56">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F56" s="1">
-        <v>52085168</v>
+        <v>3447157</v>
       </c>
       <c r="G56">
         <f t="shared" si="0"/>
-        <v>6.5277700553831372E-7</v>
+        <v>8.7028238052400862E-6</v>
       </c>
       <c r="H56">
         <f t="shared" si="1"/>
-        <v>6.5277700553831378E-2</v>
+        <v>0.87028238052400864</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B57">
         <v>30</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D57">
+        <v>14</v>
+      </c>
+      <c r="E57">
         <v>11</v>
       </c>
-      <c r="E57">
-        <v>17</v>
-      </c>
       <c r="F57" s="1">
-        <v>3447157</v>
+        <v>1830211</v>
       </c>
       <c r="G57">
         <f t="shared" si="0"/>
-        <v>8.7028238052400862E-6</v>
+        <v>1.6391552667971069E-5</v>
       </c>
       <c r="H57">
         <f t="shared" si="1"/>
-        <v>0.87028238052400864</v>
+        <v>1.639155266797107</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B58">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C58">
         <v>5</v>
       </c>
       <c r="D58">
+        <v>9</v>
+      </c>
+      <c r="E58">
         <v>14</v>
       </c>
-      <c r="E58">
+      <c r="F58" s="1">
+        <v>10247605</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>2.7323457529832579E-6</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>0.27323457529832579</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="2">
+        <v>27</v>
+      </c>
+      <c r="C59" s="2">
+        <v>3</v>
+      </c>
+      <c r="D59" s="2">
         <v>11</v>
       </c>
-      <c r="F58" s="1">
-        <v>1830211</v>
-      </c>
-      <c r="G58">
-        <f t="shared" si="0"/>
-        <v>1.6391552667971069E-5</v>
-      </c>
-      <c r="H58">
-        <f t="shared" si="1"/>
-        <v>1.639155266797107</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59">
-        <v>28</v>
-      </c>
-      <c r="C59">
+      <c r="E59" s="2">
+        <v>13</v>
+      </c>
+      <c r="F59" s="3">
+        <v>223804632</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="0"/>
+        <v>1.206409347238175E-7</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="1"/>
+        <v>1.206409347238175E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60">
+        <v>26</v>
+      </c>
+      <c r="C60">
+        <v>6</v>
+      </c>
+      <c r="D60">
+        <v>7</v>
+      </c>
+      <c r="E60">
+        <v>13</v>
+      </c>
+      <c r="F60" s="1">
+        <v>2718352</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="0"/>
+        <v>9.5646185630117064E-6</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>0.95646185630117064</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="2">
+        <v>24</v>
+      </c>
+      <c r="C61" s="2">
+        <v>7</v>
+      </c>
+      <c r="D61" s="2">
         <v>5</v>
       </c>
-      <c r="D59">
-        <v>9</v>
-      </c>
-      <c r="E59">
-        <v>14</v>
-      </c>
-      <c r="F59" s="1">
-        <v>10247605</v>
-      </c>
-      <c r="G59">
-        <f t="shared" si="0"/>
-        <v>2.7323457529832579E-6</v>
-      </c>
-      <c r="H59">
-        <f t="shared" si="1"/>
-        <v>0.27323457529832579</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="2">
-        <v>27</v>
-      </c>
-      <c r="C60" s="2">
-        <v>3</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="E61" s="2">
+        <v>12</v>
+      </c>
+      <c r="F61" s="3">
+        <v>37840044</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="0"/>
+        <v>6.3424873396024596E-7</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="1"/>
+        <v>6.3424873396024595E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62">
+        <v>24</v>
+      </c>
+      <c r="C62">
+        <v>6</v>
+      </c>
+      <c r="D62">
+        <v>7</v>
+      </c>
+      <c r="E62">
         <v>11</v>
       </c>
-      <c r="E60" s="2">
-        <v>13</v>
-      </c>
-      <c r="F60" s="3">
-        <v>223804632</v>
-      </c>
-      <c r="G60" s="2">
-        <f t="shared" si="0"/>
-        <v>1.206409347238175E-7</v>
-      </c>
-      <c r="H60" s="2">
-        <f t="shared" si="1"/>
-        <v>1.206409347238175E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B61">
-        <v>26</v>
-      </c>
-      <c r="C61">
-        <v>6</v>
-      </c>
-      <c r="D61">
-        <v>7</v>
-      </c>
-      <c r="E61">
-        <v>13</v>
-      </c>
-      <c r="F61" s="1">
-        <v>2718352</v>
-      </c>
-      <c r="G61">
-        <f t="shared" si="0"/>
-        <v>9.5646185630117064E-6</v>
-      </c>
-      <c r="H61">
-        <f t="shared" si="1"/>
-        <v>0.95646185630117064</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="2">
-        <v>24</v>
-      </c>
-      <c r="C62" s="2">
-        <v>7</v>
-      </c>
-      <c r="D62" s="2">
-        <v>5</v>
-      </c>
-      <c r="E62" s="2">
-        <v>12</v>
-      </c>
-      <c r="F62" s="3">
-        <v>37840044</v>
-      </c>
-      <c r="G62" s="2">
-        <f t="shared" si="0"/>
-        <v>6.3424873396024596E-7</v>
-      </c>
-      <c r="H62" s="2">
-        <f t="shared" si="1"/>
-        <v>6.3424873396024595E-2</v>
+      <c r="F62" s="1">
+        <v>7149077</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="0"/>
+        <v>3.35707672472964E-6</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>0.33570767247296401</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B63">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D63">
         <v>7</v>
       </c>
       <c r="E63">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" s="1">
-        <v>7149077</v>
+        <v>28838499</v>
       </c>
       <c r="G63">
         <f t="shared" si="0"/>
-        <v>3.35707672472964E-6</v>
+        <v>6.5884150211840084E-7</v>
       </c>
       <c r="H63">
         <f t="shared" si="1"/>
-        <v>0.33570767247296401</v>
+        <v>6.588415021184009E-2</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B64">
         <v>19</v>
@@ -2585,362 +2609,362 @@
         <v>3</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E64">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1">
-        <v>28838499</v>
+        <v>1534937</v>
       </c>
       <c r="G64">
         <f t="shared" si="0"/>
-        <v>6.5884150211840084E-7</v>
+        <v>1.2378358199717643E-5</v>
       </c>
       <c r="H64">
         <f t="shared" si="1"/>
-        <v>6.588415021184009E-2</v>
+        <v>1.2378358199717643</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B65">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>8</v>
+      </c>
+      <c r="E65">
+        <v>8</v>
+      </c>
+      <c r="F65" s="1">
+        <v>2777970</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="0"/>
+        <v>6.4795516150282402E-6</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>0.64795516150282406</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="2">
+        <v>17</v>
+      </c>
+      <c r="C66" s="2">
+        <v>5</v>
+      </c>
+      <c r="D66" s="2">
+        <v>4</v>
+      </c>
+      <c r="E66" s="2">
+        <v>8</v>
+      </c>
+      <c r="F66" s="3">
+        <v>45606480</v>
+      </c>
+      <c r="G66" s="2">
+        <f t="shared" si="0"/>
+        <v>3.727540472318846E-7</v>
+      </c>
+      <c r="H66" s="2">
+        <f t="shared" si="1"/>
+        <v>3.7275404723188459E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67">
+        <v>16</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>6</v>
+      </c>
+      <c r="F67" s="1">
+        <v>412623</v>
+      </c>
+      <c r="G67">
+        <f t="shared" ref="G67:G130" si="2">B67/F67</f>
+        <v>3.8776316395353625E-5</v>
+      </c>
+      <c r="H67">
+        <f t="shared" ref="H67:H130" si="3">G67*100000</f>
+        <v>3.8776316395353625</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="2">
+        <v>15</v>
+      </c>
+      <c r="C68" s="2">
+        <v>5</v>
+      </c>
+      <c r="D68" s="2">
         <v>3</v>
       </c>
-      <c r="D65">
+      <c r="E68" s="2">
+        <v>7</v>
+      </c>
+      <c r="F68" s="3">
+        <v>12458223</v>
+      </c>
+      <c r="G68" s="2">
+        <f t="shared" si="2"/>
+        <v>1.2040240409888311E-6</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" si="3"/>
+        <v>0.12040240409888311</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69">
+        <v>14</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
         <v>5</v>
       </c>
-      <c r="E65">
-        <v>11</v>
-      </c>
-      <c r="F65" s="1">
-        <v>1534937</v>
-      </c>
-      <c r="G65">
-        <f t="shared" si="0"/>
-        <v>1.2378358199717643E-5</v>
-      </c>
-      <c r="H65">
-        <f t="shared" si="1"/>
-        <v>1.2378358199717643</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66">
-        <v>18</v>
-      </c>
-      <c r="C66">
-        <v>2</v>
-      </c>
-      <c r="D66">
+      <c r="E69">
         <v>8</v>
       </c>
-      <c r="E66">
-        <v>8</v>
-      </c>
-      <c r="F66" s="1">
-        <v>2777970</v>
-      </c>
-      <c r="G66">
-        <f t="shared" si="0"/>
-        <v>6.4795516150282402E-6</v>
-      </c>
-      <c r="H66">
-        <f t="shared" si="1"/>
-        <v>0.64795516150282406</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="2">
-        <v>17</v>
-      </c>
-      <c r="C67" s="2">
-        <v>5</v>
-      </c>
-      <c r="D67" s="2">
-        <v>4</v>
-      </c>
-      <c r="E67" s="2">
-        <v>8</v>
-      </c>
-      <c r="F67" s="3">
-        <v>45606480</v>
-      </c>
-      <c r="G67" s="2">
-        <f t="shared" si="0"/>
-        <v>3.727540472318846E-7</v>
-      </c>
-      <c r="H67" s="2">
-        <f t="shared" si="1"/>
-        <v>3.7275404723188459E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>71</v>
-      </c>
-      <c r="B68">
-        <v>16</v>
-      </c>
-      <c r="C68">
-        <v>8</v>
-      </c>
-      <c r="D68">
-        <v>2</v>
-      </c>
-      <c r="E68">
-        <v>6</v>
-      </c>
-      <c r="F68" s="1">
-        <v>412623</v>
-      </c>
-      <c r="G68">
-        <f t="shared" ref="G68:G131" si="2">B68/F68</f>
-        <v>3.8776316395353625E-5</v>
-      </c>
-      <c r="H68">
-        <f t="shared" ref="H68:H131" si="3">G68*100000</f>
-        <v>3.8776316395353625</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B69" s="2">
-        <v>15</v>
-      </c>
-      <c r="C69" s="2">
-        <v>5</v>
-      </c>
-      <c r="D69" s="2">
-        <v>3</v>
-      </c>
-      <c r="E69" s="2">
-        <v>7</v>
-      </c>
-      <c r="F69" s="3">
-        <v>12458223</v>
-      </c>
-      <c r="G69" s="2">
-        <f t="shared" si="2"/>
-        <v>1.2040240409888311E-6</v>
-      </c>
-      <c r="H69" s="2">
-        <f t="shared" si="3"/>
-        <v>0.12040240409888311</v>
+      <c r="F69" s="1">
+        <v>117337368</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="2"/>
+        <v>1.1931407904087299E-7</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="3"/>
+        <v>1.19314079040873E-2</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B70">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
+        <v>8</v>
+      </c>
+      <c r="E70">
         <v>5</v>
       </c>
-      <c r="E70">
-        <v>8</v>
-      </c>
       <c r="F70" s="1">
-        <v>117337368</v>
+        <v>34308525</v>
       </c>
       <c r="G70">
         <f t="shared" si="2"/>
-        <v>1.1931407904087299E-7</v>
+        <v>3.7891457006676912E-7</v>
       </c>
       <c r="H70">
         <f t="shared" si="3"/>
-        <v>1.19314079040873E-2</v>
+        <v>3.7891457006676912E-2</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B71">
         <v>13</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1">
-        <v>34308525</v>
+        <v>19629590</v>
       </c>
       <c r="G71">
         <f t="shared" si="2"/>
-        <v>3.7891457006676912E-7</v>
+        <v>6.6226548796994743E-7</v>
       </c>
       <c r="H71">
         <f t="shared" si="3"/>
-        <v>3.7891457006676912E-2</v>
+        <v>6.6226548796994744E-2</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B72">
         <v>13</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1">
-        <v>19629590</v>
+        <v>9174520</v>
       </c>
       <c r="G72">
         <f t="shared" si="2"/>
-        <v>6.6226548796994743E-7</v>
+        <v>1.4169678631688634E-6</v>
       </c>
       <c r="H72">
         <f t="shared" si="3"/>
-        <v>6.6226548796994744E-2</v>
+        <v>0.14169678631688634</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B73">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1">
-        <v>9174520</v>
+        <v>11332972</v>
       </c>
       <c r="G73">
         <f t="shared" si="2"/>
-        <v>1.4169678631688634E-6</v>
+        <v>1.0588572882735438E-6</v>
       </c>
       <c r="H73">
         <f t="shared" si="3"/>
-        <v>0.14169678631688634</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74">
-        <v>12</v>
-      </c>
-      <c r="C74">
+        <v>0.10588572882735438</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="2">
+        <v>11</v>
+      </c>
+      <c r="C74" s="2">
+        <v>4</v>
+      </c>
+      <c r="D74" s="2">
+        <v>4</v>
+      </c>
+      <c r="E74" s="2">
         <v>3</v>
       </c>
-      <c r="D74">
-        <v>5</v>
-      </c>
-      <c r="E74">
+      <c r="F74" s="3">
+        <v>48582334</v>
+      </c>
+      <c r="G74" s="2">
+        <f t="shared" si="2"/>
+        <v>2.2641975167351984E-7</v>
+      </c>
+      <c r="H74" s="2">
+        <f t="shared" si="3"/>
+        <v>2.2641975167351985E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75">
+        <v>10</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
         <v>4</v>
       </c>
-      <c r="F74" s="1">
-        <v>11332972</v>
-      </c>
-      <c r="G74">
-        <f t="shared" si="2"/>
-        <v>1.0588572882735438E-6</v>
-      </c>
-      <c r="H74">
-        <f t="shared" si="3"/>
-        <v>0.10588572882735438</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75" s="2">
-        <v>11</v>
-      </c>
-      <c r="C75" s="2">
-        <v>4</v>
-      </c>
-      <c r="D75" s="2">
-        <v>4</v>
-      </c>
-      <c r="E75" s="2">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3">
-        <v>48582334</v>
-      </c>
-      <c r="G75" s="2">
-        <f t="shared" si="2"/>
-        <v>2.2641975167351984E-7</v>
-      </c>
-      <c r="H75" s="2">
-        <f t="shared" si="3"/>
-        <v>2.2641975167351985E-2</v>
+      <c r="F75" s="1">
+        <v>240485658</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="2"/>
+        <v>4.158252131609445E-8</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="3"/>
+        <v>4.158252131609445E-3</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B76">
         <v>10</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F76" s="1">
-        <v>240485658</v>
+        <v>3423108</v>
       </c>
       <c r="G76">
         <f t="shared" si="2"/>
-        <v>4.158252131609445E-8</v>
+        <v>2.9213217929437223E-6</v>
       </c>
       <c r="H76">
         <f t="shared" si="3"/>
-        <v>4.158252131609445E-3</v>
+        <v>0.29213217929437224</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B77">
         <v>10</v>
@@ -2955,20 +2979,20 @@
         <v>6</v>
       </c>
       <c r="F77" s="1">
-        <v>3423108</v>
+        <v>3260314</v>
       </c>
       <c r="G77">
         <f t="shared" si="2"/>
-        <v>2.9213217929437223E-6</v>
+        <v>3.0671892339204138E-6</v>
       </c>
       <c r="H77">
         <f t="shared" si="3"/>
-        <v>0.29213217929437224</v>
+        <v>0.30671892339204138</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B78">
         <v>10</v>
@@ -2983,440 +3007,440 @@
         <v>6</v>
       </c>
       <c r="F78" s="1">
-        <v>3260314</v>
+        <v>39584</v>
       </c>
       <c r="G78">
         <f t="shared" si="2"/>
-        <v>3.0671892339204138E-6</v>
+        <v>2.526273241713824E-4</v>
       </c>
       <c r="H78">
         <f t="shared" si="3"/>
-        <v>0.30671892339204138</v>
+        <v>25.262732417138238</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B79">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C79">
         <v>2</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1">
-        <v>39584</v>
+        <v>7491609</v>
       </c>
       <c r="G79">
         <f t="shared" si="2"/>
-        <v>2.526273241713824E-4</v>
+        <v>1.2013440637385106E-6</v>
       </c>
       <c r="H79">
         <f t="shared" si="3"/>
-        <v>25.262732417138238</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80">
-        <v>9</v>
-      </c>
-      <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80">
+        <v>0.12013440637385106</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="2">
+        <v>8</v>
+      </c>
+      <c r="C80" s="2">
         <v>3</v>
       </c>
-      <c r="E80">
+      <c r="D80" s="2">
         <v>4</v>
       </c>
-      <c r="F80" s="1">
-        <v>7491609</v>
-      </c>
-      <c r="G80">
-        <f t="shared" si="2"/>
-        <v>1.2013440637385106E-6</v>
-      </c>
-      <c r="H80">
-        <f t="shared" si="3"/>
-        <v>0.12013440637385106</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B81" s="2">
+      <c r="E80" s="2">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3">
+        <v>16665409</v>
+      </c>
+      <c r="G80" s="2">
+        <f t="shared" si="2"/>
+        <v>4.8003622353342785E-7</v>
+      </c>
+      <c r="H80" s="2">
+        <f t="shared" si="3"/>
+        <v>4.8003622353342788E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81">
         <v>8</v>
       </c>
-      <c r="C81" s="2">
-        <v>3</v>
-      </c>
-      <c r="D81" s="2">
-        <v>4</v>
-      </c>
-      <c r="E81" s="2">
-        <v>1</v>
-      </c>
-      <c r="F81" s="3">
-        <v>16665409</v>
-      </c>
-      <c r="G81" s="2">
-        <f t="shared" si="2"/>
-        <v>4.8003622353342785E-7</v>
-      </c>
-      <c r="H81" s="2">
-        <f t="shared" si="3"/>
-        <v>4.8003622353342788E-2</v>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>5</v>
+      </c>
+      <c r="F81" s="1">
+        <v>2716391</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="2"/>
+        <v>2.9450841208058781E-6</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="3"/>
+        <v>0.29450841208058781</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B82">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1">
-        <v>2716391</v>
+        <v>6735347</v>
       </c>
       <c r="G82">
         <f t="shared" si="2"/>
-        <v>2.9450841208058781E-6</v>
+        <v>1.0392931500040013E-6</v>
       </c>
       <c r="H82">
         <f t="shared" si="3"/>
-        <v>0.29450841208058781</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83">
-        <v>7</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-      <c r="D83">
+        <v>0.10392931500040012</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="2">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2">
         <v>3</v>
       </c>
-      <c r="E83">
+      <c r="D83" s="2">
+        <v>1</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="3">
+        <v>28647293</v>
+      </c>
+      <c r="G83" s="2">
+        <f t="shared" si="2"/>
+        <v>2.0944387310870873E-7</v>
+      </c>
+      <c r="H83" s="2">
+        <f t="shared" si="3"/>
+        <v>2.0944387310870873E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84">
+        <v>6</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
         <v>4</v>
       </c>
-      <c r="F83" s="1">
-        <v>6735347</v>
-      </c>
-      <c r="G83">
-        <f t="shared" si="2"/>
-        <v>1.0392931500040013E-6</v>
-      </c>
-      <c r="H83">
-        <f t="shared" si="3"/>
-        <v>0.10392931500040012</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B84" s="2">
-        <v>6</v>
-      </c>
-      <c r="C84" s="2">
-        <v>3</v>
-      </c>
-      <c r="D84" s="2">
-        <v>1</v>
-      </c>
-      <c r="E84" s="2">
-        <v>2</v>
-      </c>
-      <c r="F84" s="3">
-        <v>28647293</v>
-      </c>
-      <c r="G84" s="2">
-        <f t="shared" si="2"/>
-        <v>2.0944387310870873E-7</v>
-      </c>
-      <c r="H84" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0944387310870873E-2</v>
+      <c r="F84" s="1">
+        <v>3435931</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="2"/>
+        <v>1.7462515981840148E-6</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="3"/>
+        <v>0.17462515981840149</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1">
+        <v>98858950</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="2"/>
+        <v>5.0577110114966828E-8</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="3"/>
+        <v>5.0577110114966824E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="2">
+        <v>5</v>
+      </c>
+      <c r="C86" s="2">
+        <v>0</v>
+      </c>
+      <c r="D86" s="2">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2">
         <v>4</v>
       </c>
-      <c r="F85" s="1">
-        <v>3435931</v>
-      </c>
-      <c r="G85">
-        <f t="shared" si="2"/>
-        <v>1.7462515981840148E-6</v>
-      </c>
-      <c r="H85">
-        <f t="shared" si="3"/>
-        <v>0.17462515981840149</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>89</v>
-      </c>
-      <c r="B86">
+      <c r="F86" s="3">
+        <v>34121985</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="2"/>
+        <v>1.4653309296044764E-7</v>
+      </c>
+      <c r="H86" s="2">
+        <f t="shared" si="3"/>
+        <v>1.4653309296044763E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87">
         <v>5</v>
       </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-      <c r="D86">
+      <c r="C87">
         <v>3</v>
       </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-      <c r="F86" s="1">
-        <v>98858950</v>
-      </c>
-      <c r="G86">
-        <f t="shared" si="2"/>
-        <v>5.0577110114966828E-8</v>
-      </c>
-      <c r="H86">
-        <f t="shared" si="3"/>
-        <v>5.0577110114966824E-3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="2">
-        <v>5</v>
-      </c>
-      <c r="C87" s="2">
-        <v>0</v>
-      </c>
-      <c r="D87" s="2">
-        <v>1</v>
-      </c>
-      <c r="E87" s="2">
-        <v>4</v>
-      </c>
-      <c r="F87" s="3">
-        <v>34121985</v>
-      </c>
-      <c r="G87" s="2">
-        <f t="shared" si="2"/>
-        <v>1.4653309296044764E-7</v>
-      </c>
-      <c r="H87" s="2">
-        <f t="shared" si="3"/>
-        <v>1.4653309296044763E-2</v>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
+        <v>18190484</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="2"/>
+        <v>2.7486899194106103E-7</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="3"/>
+        <v>2.7486899194106105E-2</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B88">
         <v>5</v>
       </c>
       <c r="C88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F88" s="1">
-        <v>18190484</v>
+        <v>6014723</v>
       </c>
       <c r="G88">
         <f t="shared" si="2"/>
-        <v>2.7486899194106103E-7</v>
+        <v>8.3129347768799991E-7</v>
       </c>
       <c r="H88">
         <f t="shared" si="3"/>
-        <v>2.7486899194106105E-2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>92</v>
-      </c>
-      <c r="B89">
+        <v>8.3129347768799988E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="2">
         <v>5</v>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>2</v>
-      </c>
-      <c r="E89">
-        <v>2</v>
-      </c>
-      <c r="F89" s="1">
-        <v>6014723</v>
-      </c>
-      <c r="G89">
-        <f t="shared" si="2"/>
-        <v>8.3129347768799991E-7</v>
-      </c>
-      <c r="H89">
-        <f t="shared" si="3"/>
-        <v>8.3129347768799988E-2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B90" s="2">
+      <c r="C89" s="2">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2">
         <v>5</v>
       </c>
-      <c r="C90" s="2">
-        <v>0</v>
-      </c>
-      <c r="D90" s="2">
-        <v>5</v>
-      </c>
-      <c r="E90" s="2">
-        <v>0</v>
-      </c>
-      <c r="F90" s="3">
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>2604172</v>
       </c>
-      <c r="G90" s="2">
+      <c r="G89" s="2">
         <f t="shared" si="2"/>
         <v>1.9199960678480528E-6</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H89" s="2">
         <f t="shared" si="3"/>
         <v>0.19199960678480529</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90">
+        <v>4</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="F90" s="1">
+        <v>36947025</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="2"/>
+        <v>1.0826311455387815E-7</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="3"/>
+        <v>1.0826311455387816E-2</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B91">
         <v>4</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91" s="1">
-        <v>36947025</v>
+        <v>34352719</v>
       </c>
       <c r="G91">
         <f t="shared" si="2"/>
-        <v>1.0826311455387815E-7</v>
+        <v>1.1643910923033487E-7</v>
       </c>
       <c r="H91">
         <f t="shared" si="3"/>
-        <v>1.0826311455387816E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>95</v>
-      </c>
-      <c r="B92">
+        <v>1.1643910923033487E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="2">
         <v>4</v>
       </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92">
-        <v>3</v>
-      </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92" s="1">
-        <v>34352719</v>
-      </c>
-      <c r="G92">
-        <f t="shared" si="2"/>
-        <v>1.1643910923033487E-7</v>
-      </c>
-      <c r="H92">
-        <f t="shared" si="3"/>
-        <v>1.1643910923033487E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B93" s="2">
+      <c r="C92" s="2">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2">
+        <v>2</v>
+      </c>
+      <c r="F92" s="3">
+        <v>28873034</v>
+      </c>
+      <c r="G92" s="2">
+        <f t="shared" si="2"/>
+        <v>1.385375710775667E-7</v>
+      </c>
+      <c r="H92" s="2">
+        <f t="shared" si="3"/>
+        <v>1.3853757107756669E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93">
         <v>4</v>
       </c>
-      <c r="C93" s="2">
-        <v>1</v>
-      </c>
-      <c r="D93" s="2">
-        <v>1</v>
-      </c>
-      <c r="E93" s="2">
-        <v>2</v>
-      </c>
-      <c r="F93" s="3">
-        <v>28873034</v>
-      </c>
-      <c r="G93" s="2">
-        <f t="shared" si="2"/>
-        <v>1.385375710775667E-7</v>
-      </c>
-      <c r="H93" s="2">
-        <f t="shared" si="3"/>
-        <v>1.3853757107756669E-2</v>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93" s="1">
+        <v>23227014</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="2"/>
+        <v>1.7221326856736729E-7</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="3"/>
+        <v>1.7221326856736729E-2</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B94">
         <v>4</v>
@@ -3431,188 +3455,188 @@
         <v>2</v>
       </c>
       <c r="F94" s="1">
-        <v>23227014</v>
+        <v>10143543</v>
       </c>
       <c r="G94">
         <f t="shared" si="2"/>
-        <v>1.7221326856736729E-7</v>
+        <v>3.9433953205502259E-7</v>
       </c>
       <c r="H94">
         <f t="shared" si="3"/>
-        <v>1.7221326856736729E-2</v>
+        <v>3.9433953205502262E-2</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B95">
         <v>4</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95">
         <v>2</v>
       </c>
       <c r="F95" s="1">
-        <v>10143543</v>
+        <v>5353930</v>
       </c>
       <c r="G95">
         <f t="shared" si="2"/>
-        <v>3.9433953205502259E-7</v>
+        <v>7.4711473627783708E-7</v>
       </c>
       <c r="H95">
         <f t="shared" si="3"/>
-        <v>3.9433953205502262E-2</v>
+        <v>7.4711473627783714E-2</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B96">
         <v>4</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96">
         <v>2</v>
       </c>
       <c r="F96" s="1">
-        <v>5353930</v>
+        <v>5212173</v>
       </c>
       <c r="G96">
         <f t="shared" si="2"/>
-        <v>7.4711473627783708E-7</v>
+        <v>7.6743423520286073E-7</v>
       </c>
       <c r="H96">
         <f t="shared" si="3"/>
-        <v>7.4711473627783714E-2</v>
+        <v>7.6743423520286069E-2</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B97">
         <v>4</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>5212173</v>
+        <v>1485509</v>
       </c>
       <c r="G97">
         <f t="shared" si="2"/>
-        <v>7.6743423520286073E-7</v>
+        <v>2.6926797481536631E-6</v>
       </c>
       <c r="H97">
         <f t="shared" si="3"/>
-        <v>7.6743423520286069E-2</v>
+        <v>0.2692679748153663</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B98">
         <v>4</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98" s="1">
-        <v>1485509</v>
+        <v>654768</v>
       </c>
       <c r="G98">
         <f t="shared" si="2"/>
-        <v>2.6926797481536631E-6</v>
+        <v>6.1090340395376683E-6</v>
       </c>
       <c r="H98">
         <f t="shared" si="3"/>
-        <v>0.2692679748153663</v>
+        <v>0.61090340395376685</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B99">
         <v>4</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" s="1">
-        <v>654768</v>
+        <v>375318</v>
       </c>
       <c r="G99">
         <f t="shared" si="2"/>
-        <v>6.1090340395376683E-6</v>
+        <v>1.0657628997276976E-5</v>
       </c>
       <c r="H99">
         <f t="shared" si="3"/>
-        <v>0.61090340395376685</v>
+        <v>1.0657628997276976</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="1">
-        <v>375318</v>
+        <v>11337052</v>
       </c>
       <c r="G100">
         <f t="shared" si="2"/>
-        <v>1.0657628997276976E-5</v>
+        <v>2.6461905617086345E-7</v>
       </c>
       <c r="H100">
         <f t="shared" si="3"/>
-        <v>1.0657628997276976</v>
+        <v>2.6461905617086345E-2</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B101">
         <v>3</v>
@@ -3621,474 +3645,474 @@
         <v>1</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="1">
-        <v>11337052</v>
+        <v>4468087</v>
       </c>
       <c r="G101">
         <f t="shared" si="2"/>
-        <v>2.6461905617086345E-7</v>
+        <v>6.7142828687086893E-7</v>
       </c>
       <c r="H101">
         <f t="shared" si="3"/>
-        <v>2.6461905617086345E-2</v>
+        <v>6.7142828687086889E-2</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B102">
         <v>3</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="1">
-        <v>4468087</v>
+        <v>4310108</v>
       </c>
       <c r="G102">
         <f t="shared" si="2"/>
-        <v>6.7142828687086893E-7</v>
+        <v>6.9603824312523023E-7</v>
       </c>
       <c r="H102">
         <f t="shared" si="3"/>
-        <v>6.7142828687086889E-2</v>
+        <v>6.960382431252303E-2</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B103">
         <v>3</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" s="1">
-        <v>4310108</v>
+        <v>936375</v>
       </c>
       <c r="G103">
         <f t="shared" si="2"/>
-        <v>6.9603824312523023E-7</v>
+        <v>3.2038446135362435E-6</v>
       </c>
       <c r="H103">
         <f t="shared" si="3"/>
-        <v>6.960382431252303E-2</v>
+        <v>0.32038446135362436</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>1</v>
       </c>
       <c r="F104" s="1">
-        <v>936375</v>
+        <v>126183</v>
       </c>
       <c r="G104">
         <f t="shared" si="2"/>
-        <v>3.2038446135362435E-6</v>
+        <v>2.3774993461876799E-5</v>
       </c>
       <c r="H104">
         <f t="shared" si="3"/>
-        <v>0.32038446135362436</v>
+        <v>2.3774993461876801</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B105">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="1">
-        <v>126183</v>
+        <v>33642</v>
       </c>
       <c r="G105">
         <f t="shared" si="2"/>
-        <v>2.3774993461876799E-5</v>
+        <v>8.9174246477617271E-5</v>
       </c>
       <c r="H105">
         <f t="shared" si="3"/>
-        <v>2.3774993461876801</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>109</v>
-      </c>
-      <c r="B106">
-        <v>3</v>
-      </c>
-      <c r="C106">
-        <v>0</v>
-      </c>
-      <c r="D106">
-        <v>1</v>
-      </c>
-      <c r="E106">
-        <v>2</v>
-      </c>
-      <c r="F106" s="1">
-        <v>33642</v>
-      </c>
-      <c r="G106">
-        <f t="shared" si="2"/>
-        <v>8.9174246477617271E-5</v>
-      </c>
-      <c r="H106">
-        <f t="shared" si="3"/>
         <v>8.9174246477617274</v>
       </c>
     </row>
-    <row r="107" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="2" t="s">
+    <row r="106" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B107" s="2">
-        <v>2</v>
-      </c>
-      <c r="C107" s="2">
-        <v>0</v>
-      </c>
-      <c r="D107" s="2">
-        <v>2</v>
-      </c>
-      <c r="E107" s="2">
-        <v>0</v>
-      </c>
-      <c r="F107" s="3">
+      <c r="B106" s="2">
+        <v>2</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3">
         <v>67438106</v>
       </c>
-      <c r="G107" s="2">
+      <c r="G106" s="2">
         <f t="shared" si="2"/>
         <v>2.965682339892523E-8</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H106" s="2">
         <f t="shared" si="3"/>
         <v>2.9656823398925228E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>111</v>
       </c>
-      <c r="B108">
-        <v>2</v>
-      </c>
-      <c r="C108">
-        <v>0</v>
-      </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-      <c r="E108">
-        <v>2</v>
-      </c>
-      <c r="F108" s="1">
+      <c r="B107">
+        <v>2</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107" s="1">
         <v>42239854</v>
       </c>
-      <c r="G108">
+      <c r="G107">
         <f t="shared" si="2"/>
         <v>4.7348648506218795E-8</v>
       </c>
-      <c r="H108">
+      <c r="H107">
         <f t="shared" si="3"/>
         <v>4.7348648506218794E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B108" s="2">
+        <v>2</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1</v>
+      </c>
+      <c r="D108" s="2">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3">
+        <v>33897354</v>
+      </c>
+      <c r="G108" s="2">
+        <f t="shared" si="2"/>
+        <v>5.9001655409445821E-8</v>
+      </c>
+      <c r="H108" s="2">
+        <f t="shared" si="3"/>
+        <v>5.9001655409445823E-3</v>
       </c>
     </row>
     <row r="109" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B109" s="2">
         <v>2</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="2">
         <v>1</v>
       </c>
       <c r="F109" s="3">
-        <v>33897354</v>
+        <v>27202843</v>
       </c>
       <c r="G109" s="2">
         <f t="shared" si="2"/>
-        <v>5.9001655409445821E-8</v>
+        <v>7.352172712241879E-8</v>
       </c>
       <c r="H109" s="2">
         <f t="shared" si="3"/>
-        <v>5.9001655409445823E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B110" s="2">
-        <v>2</v>
-      </c>
-      <c r="C110" s="2">
-        <v>0</v>
-      </c>
-      <c r="D110" s="2">
-        <v>1</v>
-      </c>
-      <c r="E110" s="2">
-        <v>1</v>
-      </c>
-      <c r="F110" s="3">
-        <v>27202843</v>
-      </c>
-      <c r="G110" s="2">
-        <f t="shared" si="2"/>
-        <v>7.352172712241879E-8</v>
-      </c>
-      <c r="H110" s="2">
-        <f t="shared" si="3"/>
         <v>7.3521727122418789E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>114</v>
       </c>
-      <c r="B111">
-        <v>2</v>
-      </c>
-      <c r="C111">
-        <v>0</v>
-      </c>
-      <c r="D111">
-        <v>2</v>
-      </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-      <c r="F111" s="1">
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>2</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1">
         <v>21893579</v>
       </c>
-      <c r="G111">
+      <c r="G110">
         <f t="shared" si="2"/>
         <v>9.1350984688250378E-8</v>
       </c>
-      <c r="H111">
+      <c r="H110">
         <f t="shared" si="3"/>
         <v>9.1350984688250373E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111" s="2">
+        <v>2</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
+        <v>1</v>
+      </c>
+      <c r="E111" s="2">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3">
+        <v>20569737</v>
+      </c>
+      <c r="G111" s="2">
+        <f t="shared" si="2"/>
+        <v>9.7230217381972364E-8</v>
+      </c>
+      <c r="H111" s="2">
+        <f t="shared" si="3"/>
+        <v>9.7230217381972361E-3</v>
       </c>
     </row>
     <row r="112" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B112" s="2">
         <v>2</v>
       </c>
       <c r="C112" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" s="2">
         <v>1</v>
       </c>
       <c r="E112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="3">
-        <v>20569737</v>
+        <v>13238559</v>
       </c>
       <c r="G112" s="2">
         <f t="shared" si="2"/>
-        <v>9.7230217381972364E-8</v>
+        <v>1.510738442152201E-7</v>
       </c>
       <c r="H112" s="2">
         <f t="shared" si="3"/>
-        <v>9.7230217381972361E-3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B113" s="2">
-        <v>2</v>
-      </c>
-      <c r="C113" s="2">
-        <v>1</v>
-      </c>
-      <c r="D113" s="2">
-        <v>1</v>
-      </c>
-      <c r="E113" s="2">
-        <v>0</v>
-      </c>
-      <c r="F113" s="3">
-        <v>13238559</v>
-      </c>
-      <c r="G113" s="2">
-        <f t="shared" si="2"/>
-        <v>1.510738442152201E-7</v>
-      </c>
-      <c r="H113" s="2">
-        <f t="shared" si="3"/>
         <v>1.510738442152201E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>117</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113" s="1">
+        <v>11724763</v>
+      </c>
+      <c r="G113">
+        <f t="shared" si="2"/>
+        <v>1.7057914091738998E-7</v>
+      </c>
+      <c r="H113">
+        <f t="shared" si="3"/>
+        <v>1.7057914091738999E-2</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>1</v>
       </c>
       <c r="F114" s="1">
-        <v>11724763</v>
+        <v>9516871</v>
       </c>
       <c r="G114">
         <f t="shared" si="2"/>
-        <v>1.7057914091738998E-7</v>
+        <v>2.1015310599460684E-7</v>
       </c>
       <c r="H114">
         <f t="shared" si="3"/>
-        <v>1.7057914091738999E-2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>118</v>
-      </c>
-      <c r="B115">
-        <v>2</v>
-      </c>
-      <c r="C115">
-        <v>1</v>
-      </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="E115">
-        <v>1</v>
-      </c>
-      <c r="F115" s="1">
-        <v>9516871</v>
-      </c>
-      <c r="G115">
-        <f t="shared" si="2"/>
-        <v>2.1015310599460684E-7</v>
-      </c>
-      <c r="H115">
-        <f t="shared" si="3"/>
         <v>2.1015310599460685E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="2" t="s">
+    <row r="115" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B116" s="2">
-        <v>2</v>
-      </c>
-      <c r="C116" s="2">
-        <v>0</v>
-      </c>
-      <c r="D116" s="2">
-        <v>1</v>
-      </c>
-      <c r="E116" s="2">
-        <v>1</v>
-      </c>
-      <c r="F116" s="3">
+      <c r="B115" s="2">
+        <v>2</v>
+      </c>
+      <c r="C115" s="2">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1</v>
+      </c>
+      <c r="E115" s="2">
+        <v>1</v>
+      </c>
+      <c r="F115" s="3">
         <v>2675352</v>
       </c>
-      <c r="G116" s="2">
+      <c r="G115" s="2">
         <f t="shared" si="2"/>
         <v>7.4756518020806237E-7</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H115" s="2">
         <f t="shared" si="3"/>
         <v>7.475651802080624E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116" s="1">
+        <v>2085679</v>
+      </c>
+      <c r="G116">
+        <f t="shared" si="2"/>
+        <v>9.589203324193225E-7</v>
+      </c>
+      <c r="H116">
+        <f t="shared" si="3"/>
+        <v>9.5892033241932254E-2</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>1</v>
       </c>
       <c r="F117" s="1">
-        <v>2085679</v>
+        <v>623236</v>
       </c>
       <c r="G117">
         <f t="shared" si="2"/>
-        <v>9.589203324193225E-7</v>
+        <v>3.2090572431631037E-6</v>
       </c>
       <c r="H117">
         <f t="shared" si="3"/>
-        <v>9.5892033241932254E-2</v>
+        <v>0.32090572431631037</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -4103,160 +4127,160 @@
         <v>1</v>
       </c>
       <c r="F118" s="1">
-        <v>623236</v>
+        <v>64069</v>
       </c>
       <c r="G118">
         <f t="shared" si="2"/>
-        <v>3.2090572431631037E-6</v>
+        <v>3.1216344878178215E-5</v>
       </c>
       <c r="H118">
         <f t="shared" si="3"/>
-        <v>0.32090572431631037</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>122</v>
-      </c>
-      <c r="B119">
-        <v>2</v>
-      </c>
-      <c r="C119">
-        <v>1</v>
-      </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="E119">
-        <v>1</v>
-      </c>
-      <c r="F119" s="1">
-        <v>64069</v>
-      </c>
-      <c r="G119">
-        <f t="shared" si="2"/>
-        <v>3.1216344878178215E-5</v>
-      </c>
-      <c r="H119">
-        <f t="shared" si="3"/>
         <v>3.1216344878178215</v>
       </c>
     </row>
-    <row r="120" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="2" t="s">
+    <row r="119" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B120" s="2">
-        <v>1</v>
-      </c>
-      <c r="C120" s="2">
-        <v>0</v>
-      </c>
-      <c r="D120" s="2">
-        <v>1</v>
-      </c>
-      <c r="E120" s="2">
-        <v>0</v>
-      </c>
-      <c r="F120" s="3">
+      <c r="B119" s="2">
+        <v>1</v>
+      </c>
+      <c r="C119" s="2">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2">
+        <v>1</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3">
         <v>48109006</v>
       </c>
-      <c r="G120" s="2">
+      <c r="G119" s="2">
         <f t="shared" si="2"/>
         <v>2.0786128900688573E-8</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H119" s="2">
         <f t="shared" si="3"/>
         <v>2.0786128900688572E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>124</v>
       </c>
-      <c r="B121">
-        <v>1</v>
-      </c>
-      <c r="C121">
-        <v>0</v>
-      </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="E121">
-        <v>1</v>
-      </c>
-      <c r="F121" s="1">
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120" s="1">
         <v>45504560</v>
       </c>
-      <c r="G121">
+      <c r="G120">
         <f t="shared" si="2"/>
         <v>2.1975819566214903E-8</v>
       </c>
-      <c r="H121">
+      <c r="H120">
         <f t="shared" si="3"/>
         <v>2.1975819566214905E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="2" t="s">
+    <row r="121" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B122" s="2">
-        <v>1</v>
-      </c>
-      <c r="C122" s="2">
-        <v>0</v>
-      </c>
-      <c r="D122" s="2">
-        <v>0</v>
-      </c>
-      <c r="E122" s="2">
-        <v>1</v>
-      </c>
-      <c r="F122" s="3">
+      <c r="B121" s="2">
+        <v>1</v>
+      </c>
+      <c r="C121" s="2">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" s="2">
+        <v>1</v>
+      </c>
+      <c r="F121" s="3">
         <v>23251485</v>
       </c>
-      <c r="G122" s="2">
+      <c r="G121" s="2">
         <f t="shared" si="2"/>
         <v>4.300800572522572E-8</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H121" s="2">
         <f t="shared" si="3"/>
         <v>4.3008005725225723E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>126</v>
       </c>
-      <c r="B123">
-        <v>1</v>
-      </c>
-      <c r="C123">
-        <v>0</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123">
-        <v>0</v>
-      </c>
-      <c r="F123" s="1">
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122" s="1">
         <v>18092026</v>
       </c>
-      <c r="G123">
+      <c r="G122">
         <f t="shared" si="2"/>
         <v>5.5272969428631158E-8</v>
       </c>
-      <c r="H123">
+      <c r="H122">
         <f t="shared" si="3"/>
         <v>5.5272969428631158E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B123" s="2">
+        <v>1</v>
+      </c>
+      <c r="C123" s="2">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2">
+        <v>1</v>
+      </c>
+      <c r="E123" s="2">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3">
+        <v>17763163</v>
+      </c>
+      <c r="G123" s="2">
+        <f t="shared" si="2"/>
+        <v>5.6296280116328381E-8</v>
+      </c>
+      <c r="H123" s="2">
+        <f t="shared" si="3"/>
+        <v>5.6296280116328382E-3</v>
       </c>
     </row>
     <row r="124" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B124" s="2">
         <v>1</v>
@@ -4265,54 +4289,54 @@
         <v>0</v>
       </c>
       <c r="D124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="3">
-        <v>17763163</v>
+        <v>9053799</v>
       </c>
       <c r="G124" s="2">
         <f t="shared" si="2"/>
-        <v>5.6296280116328381E-8</v>
+        <v>1.1045087261159653E-7</v>
       </c>
       <c r="H124" s="2">
         <f t="shared" si="3"/>
-        <v>5.6296280116328382E-3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B125" s="2">
-        <v>1</v>
-      </c>
-      <c r="C125" s="2">
-        <v>0</v>
-      </c>
-      <c r="D125" s="2">
-        <v>0</v>
-      </c>
-      <c r="E125" s="2">
-        <v>1</v>
-      </c>
-      <c r="F125" s="3">
-        <v>9053799</v>
-      </c>
-      <c r="G125" s="2">
-        <f t="shared" si="2"/>
-        <v>1.1045087261159653E-7</v>
-      </c>
-      <c r="H125" s="2">
-        <f t="shared" si="3"/>
         <v>1.1045087261159653E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>129</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125" s="1">
+        <v>6861524</v>
+      </c>
+      <c r="G125">
+        <f t="shared" si="2"/>
+        <v>1.4574021747938213E-7</v>
+      </c>
+      <c r="H125">
+        <f t="shared" si="3"/>
+        <v>1.4574021747938213E-2</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -4327,48 +4351,48 @@
         <v>0</v>
       </c>
       <c r="F126" s="1">
-        <v>6861524</v>
+        <v>6516100</v>
       </c>
       <c r="G126">
         <f t="shared" si="2"/>
-        <v>1.4574021747938213E-7</v>
+        <v>1.5346603029419438E-7</v>
       </c>
       <c r="H126">
         <f t="shared" si="3"/>
-        <v>1.4574021747938213E-2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>130</v>
-      </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127">
-        <v>0</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-      <c r="F127" s="1">
-        <v>6516100</v>
-      </c>
-      <c r="G127">
-        <f t="shared" si="2"/>
-        <v>1.5346603029419438E-7</v>
-      </c>
-      <c r="H127">
-        <f t="shared" si="3"/>
         <v>1.5346603029419438E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B127" s="2">
+        <v>1</v>
+      </c>
+      <c r="C127" s="2">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2">
+        <v>1</v>
+      </c>
+      <c r="F127" s="3">
+        <v>3748901</v>
+      </c>
+      <c r="G127" s="2">
+        <f t="shared" si="2"/>
+        <v>2.6674484068797763E-7</v>
+      </c>
+      <c r="H127" s="2">
+        <f t="shared" si="3"/>
+        <v>2.6674484068797764E-2</v>
       </c>
     </row>
     <row r="128" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B128" s="2">
         <v>1</v>
@@ -4377,26 +4401,26 @@
         <v>0</v>
       </c>
       <c r="D128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" s="3">
-        <v>3748901</v>
+        <v>2436566</v>
       </c>
       <c r="G128" s="2">
         <f t="shared" si="2"/>
-        <v>2.6674484068797763E-7</v>
+        <v>4.1041367235691545E-7</v>
       </c>
       <c r="H128" s="2">
         <f t="shared" si="3"/>
-        <v>2.6674484068797764E-2</v>
+        <v>4.1041367235691545E-2</v>
       </c>
     </row>
     <row r="129" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B129" s="2">
         <v>1</v>
@@ -4405,110 +4429,110 @@
         <v>0</v>
       </c>
       <c r="D129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="3">
-        <v>2436566</v>
+        <v>1300557</v>
       </c>
       <c r="G129" s="2">
         <f t="shared" si="2"/>
-        <v>4.1041367235691545E-7</v>
+        <v>7.6890132458631186E-7</v>
       </c>
       <c r="H129" s="2">
         <f t="shared" si="3"/>
-        <v>4.1041367235691545E-2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B130" s="2">
-        <v>1</v>
-      </c>
-      <c r="C130" s="2">
-        <v>0</v>
-      </c>
-      <c r="D130" s="2">
-        <v>0</v>
-      </c>
-      <c r="E130" s="2">
-        <v>1</v>
-      </c>
-      <c r="F130" s="3">
-        <v>1300557</v>
-      </c>
-      <c r="G130" s="2">
-        <f t="shared" si="2"/>
-        <v>7.6890132458631186E-7</v>
-      </c>
-      <c r="H130" s="2">
-        <f t="shared" si="3"/>
         <v>7.6890132458631189E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>134</v>
       </c>
-      <c r="B131">
-        <v>1</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
-      <c r="F131" s="1">
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130" s="1">
         <v>1260138</v>
       </c>
-      <c r="G131">
+      <c r="G130">
         <f t="shared" si="2"/>
         <v>7.9356387951160902E-7</v>
       </c>
-      <c r="H131">
+      <c r="H130">
         <f t="shared" si="3"/>
         <v>7.93563879511609E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="2" t="s">
+    <row r="131" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B132" s="2">
-        <v>1</v>
-      </c>
-      <c r="C132" s="2">
-        <v>0</v>
-      </c>
-      <c r="D132" s="2">
-        <v>0</v>
-      </c>
-      <c r="E132" s="2">
-        <v>1</v>
-      </c>
-      <c r="F132" s="3">
+      <c r="B131" s="2">
+        <v>1</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0</v>
+      </c>
+      <c r="E131" s="2">
+        <v>1</v>
+      </c>
+      <c r="F131" s="3">
         <v>1136455</v>
       </c>
-      <c r="G132" s="2">
-        <f t="shared" ref="G132:G137" si="4">B132/F132</f>
+      <c r="G131" s="2">
+        <f t="shared" ref="G131:G136" si="4">B131/F131</f>
         <v>8.7992925368800353E-7</v>
       </c>
-      <c r="H132" s="2">
-        <f t="shared" ref="H132:H137" si="5">G132*100000</f>
+      <c r="H131" s="2">
+        <f t="shared" ref="H131:H136" si="5">G131*100000</f>
         <v>8.7992925368800351E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>136</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132" s="1">
+        <v>813834</v>
+      </c>
+      <c r="G132">
+        <f t="shared" si="4"/>
+        <v>1.2287518093370393E-6</v>
+      </c>
+      <c r="H132">
+        <f t="shared" si="5"/>
+        <v>0.12287518093370392</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -4517,26 +4541,26 @@
         <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="1">
-        <v>813834</v>
+        <v>626485</v>
       </c>
       <c r="G133">
         <f t="shared" si="4"/>
-        <v>1.2287518093370393E-6</v>
+        <v>1.5962074111910101E-6</v>
       </c>
       <c r="H133">
         <f t="shared" si="5"/>
-        <v>0.12287518093370392</v>
+        <v>0.15962074111910102</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -4545,26 +4569,26 @@
         <v>0</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="1">
-        <v>626485</v>
+        <v>281995</v>
       </c>
       <c r="G134">
         <f t="shared" si="4"/>
-        <v>1.5962074111910101E-6</v>
+        <v>3.546162165995851E-6</v>
       </c>
       <c r="H134">
         <f t="shared" si="5"/>
-        <v>0.15962074111910102</v>
+        <v>0.35461621659958509</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -4573,26 +4597,26 @@
         <v>0</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="1">
-        <v>281995</v>
+        <v>225681</v>
       </c>
       <c r="G135">
         <f t="shared" si="4"/>
-        <v>3.546162165995851E-6</v>
+        <v>4.4310331840075154E-6</v>
       </c>
       <c r="H135">
         <f t="shared" si="5"/>
-        <v>0.35461621659958509</v>
+        <v>0.44310331840075157</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -4607,41 +4631,13 @@
         <v>0</v>
       </c>
       <c r="F136" s="1">
-        <v>225681</v>
+        <v>107773</v>
       </c>
       <c r="G136">
         <f t="shared" si="4"/>
-        <v>4.4310331840075154E-6</v>
+        <v>9.2787618420198014E-6</v>
       </c>
       <c r="H136">
-        <f t="shared" si="5"/>
-        <v>0.44310331840075157</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>140</v>
-      </c>
-      <c r="B137">
-        <v>1</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>1</v>
-      </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
-      <c r="F137" s="1">
-        <v>107773</v>
-      </c>
-      <c r="G137">
-        <f t="shared" si="4"/>
-        <v>9.2787618420198014E-6</v>
-      </c>
-      <c r="H137">
         <f t="shared" si="5"/>
         <v>0.92787618420198015</v>
       </c>
@@ -4660,7 +4656,7 @@
     <col min="2" max="2" width="17.81640625" customWidth="1"/>
     <col min="6" max="6" width="16.90625" customWidth="1"/>
     <col min="7" max="7" width="19.08984375" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -4683,10 +4679,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
